--- a/ru/downloads/data-excel/10.b.1.1.xlsx
+++ b/ru/downloads/data-excel/10.b.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BC4FBD-445F-4D55-8056-E2407733661D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,9 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
-    <t>10.b.1 Совокупный объем потоков ресурсов в целях развития в разбивке по странам-получателям и странам-донорам и видам потоков*</t>
-  </si>
-  <si>
     <t>(млн.сом)</t>
   </si>
   <si>
@@ -77,13 +75,16 @@
   </si>
   <si>
     <t>*по данным МФ КР</t>
+  </si>
+  <si>
+    <t>10.b.1.1 Совокупный объем потоков ресурсов в целях развития в разбивке по странам-получателям и видам потоков*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +119,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -148,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -162,14 +186,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -189,9 +225,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -229,9 +265,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,7 +302,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -301,7 +337,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -474,25 +510,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="3" width="40.140625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="51" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -503,460 +543,689 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>2013</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2014</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2015</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2017</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2018</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2019</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2020</v>
+      </c>
+      <c r="L4" s="3">
+        <v>2021</v>
+      </c>
+      <c r="M4" s="3">
+        <v>2022</v>
+      </c>
+      <c r="N4" s="3">
+        <v>2023</v>
+      </c>
+      <c r="O4" s="3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>2013</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2014</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2015</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2016</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2017</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2018</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2019</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2020</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+    </row>
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="D6" s="1">
+        <v>488.2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>521.29999999999995</v>
+      </c>
+      <c r="F6" s="1">
+        <v>758</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1034.8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1569.2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2283.9</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1778.1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1333.83</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1221.02</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1497.61</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1143.5999999999999</v>
+      </c>
+      <c r="O6" s="1">
+        <v>5330.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
-        <v>488.2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>521.29999999999995</v>
-      </c>
-      <c r="D6" s="1">
-        <v>758</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1034.8</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1569.2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2283.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="D7" s="1">
+        <v>4295</v>
+      </c>
+      <c r="E7" s="1">
+        <v>9576.2999999999993</v>
+      </c>
+      <c r="F7" s="1">
+        <v>7552.8</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10221.799999999999</v>
+      </c>
+      <c r="H7" s="1">
+        <v>14436.4</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5471</v>
+      </c>
+      <c r="J7" s="1">
+        <v>7926.56</v>
+      </c>
+      <c r="K7" s="1">
+        <v>4294.3</v>
+      </c>
+      <c r="L7" s="1">
+        <v>7544.6</v>
+      </c>
+      <c r="M7" s="1">
+        <v>12582.13</v>
+      </c>
+      <c r="N7" s="1">
+        <v>9428.7999999999993</v>
+      </c>
+      <c r="O7" s="1">
+        <v>10004.200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1">
-        <v>4295</v>
-      </c>
-      <c r="C7" s="1">
-        <v>9576.2999999999993</v>
-      </c>
-      <c r="D7" s="1">
-        <v>7552.8</v>
-      </c>
-      <c r="E7" s="1">
-        <v>10221.799999999999</v>
-      </c>
-      <c r="F7" s="1">
-        <v>14436.4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5471</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="D8" s="1">
+        <v>9828.6</v>
+      </c>
+      <c r="E8" s="1">
+        <v>11570.1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1603.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10411.700000000001</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8104.8</v>
+      </c>
+      <c r="I8" s="1">
+        <v>3356.2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4979.5600000000004</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3625.55</v>
+      </c>
+      <c r="L8" s="1">
+        <v>8224.07</v>
+      </c>
+      <c r="M8" s="1">
+        <v>6466.32</v>
+      </c>
+      <c r="N8" s="1">
+        <v>8877.5</v>
+      </c>
+      <c r="O8" s="1">
+        <v>6645.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
-        <v>9828.6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>11570.1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1603.2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>10411.700000000001</v>
-      </c>
-      <c r="F8" s="1">
-        <v>8104.8</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3356.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="D9" s="1">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>64</v>
+      </c>
+      <c r="F9" s="1">
+        <v>77.7</v>
+      </c>
+      <c r="G9" s="1">
+        <v>77.2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>383.9</v>
+      </c>
+      <c r="I9" s="1">
+        <v>351.7</v>
+      </c>
+      <c r="J9" s="1">
+        <v>123.42</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1187.05</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1833.14</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1609.9</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1236.5999999999999</v>
+      </c>
+      <c r="O9" s="1">
+        <v>614.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1">
-        <v>129.80000000000001</v>
-      </c>
-      <c r="C9" s="1">
-        <v>64</v>
-      </c>
-      <c r="D9" s="1">
-        <v>77.7</v>
-      </c>
-      <c r="E9" s="1">
-        <v>77.2</v>
-      </c>
-      <c r="F9" s="1">
-        <v>383.9</v>
-      </c>
-      <c r="G9" s="1">
-        <v>351.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="D10" s="1">
+        <v>118.8</v>
+      </c>
+      <c r="E10" s="1">
+        <v>224.9</v>
+      </c>
+      <c r="F10" s="1">
+        <v>409.5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>555.70000000000005</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1129</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1129.2</v>
+      </c>
+      <c r="J10" s="1">
+        <v>337.39</v>
+      </c>
+      <c r="K10" s="1">
+        <v>190.48</v>
+      </c>
+      <c r="L10" s="1">
+        <v>544.20000000000005</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1684.44</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1568.5</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1422.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
-        <v>118.8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>224.9</v>
-      </c>
-      <c r="D10" s="1">
-        <v>409.5</v>
-      </c>
-      <c r="E10" s="1">
-        <v>555.70000000000005</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1129</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1129.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="D11" s="1">
+        <v>92</v>
+      </c>
+      <c r="E11" s="1">
+        <v>55.1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>38</v>
+      </c>
+      <c r="G11" s="1">
+        <v>140.4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>141.69999999999999</v>
+      </c>
+      <c r="I11" s="1">
+        <v>46.7</v>
+      </c>
+      <c r="J11" s="1">
+        <v>38.659999999999997</v>
+      </c>
+      <c r="K11" s="1">
+        <v>108.18</v>
+      </c>
+      <c r="L11" s="1">
+        <v>195.87</v>
+      </c>
+      <c r="M11" s="1">
+        <v>244.38</v>
+      </c>
+      <c r="N11" s="1">
+        <v>575.5</v>
+      </c>
+      <c r="O11" s="1">
+        <v>244.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1">
-        <v>92</v>
-      </c>
-      <c r="C11" s="1">
-        <v>55.1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>38</v>
-      </c>
-      <c r="E11" s="1">
-        <v>140.4</v>
-      </c>
-      <c r="F11" s="1">
-        <v>141.69999999999999</v>
-      </c>
-      <c r="G11" s="1">
-        <v>46.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="D12" s="1">
+        <v>887.8</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1398.3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1393.5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1602.5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2023.3</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1960.2</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2237.15</v>
+      </c>
+      <c r="K12" s="1">
+        <v>4041.45</v>
+      </c>
+      <c r="L12" s="1">
+        <v>54353.83</v>
+      </c>
+      <c r="M12" s="1">
+        <v>3943.41</v>
+      </c>
+      <c r="N12" s="1">
+        <v>7084.6</v>
+      </c>
+      <c r="O12" s="1">
+        <v>5441.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
-        <v>887.8</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1398.3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1393.5</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1602.5</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2023.3</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1960.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="D13" s="1">
+        <v>1600.3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1082.5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>683.1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>127.1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>101</v>
+      </c>
+      <c r="I13" s="1">
+        <v>225.7</v>
+      </c>
+      <c r="J13" s="1">
+        <v>894.59</v>
+      </c>
+      <c r="K13" s="1">
+        <v>910.72</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2514.42</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4337.3100000000004</v>
+      </c>
+      <c r="N13" s="1">
+        <v>9681.5</v>
+      </c>
+      <c r="O13" s="1">
+        <v>5466.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1">
-        <v>1600.3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1082.5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>683.1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>127.1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>101</v>
-      </c>
-      <c r="G13" s="1">
-        <v>225.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="D15" s="1">
+        <v>10956.3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>18162.900000000001</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3595.7</v>
+      </c>
+      <c r="G15" s="1">
+        <v>17189.8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16804.7</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2995.2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6659.9</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1057.74</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2539.77</v>
+      </c>
+      <c r="M15" s="1">
+        <v>6119.3</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1780</v>
+      </c>
+      <c r="O15" s="1">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1">
-        <v>10956.3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>18162.900000000001</v>
-      </c>
-      <c r="D15" s="1">
-        <v>3595.7</v>
-      </c>
-      <c r="E15" s="1">
-        <v>17189.8</v>
-      </c>
-      <c r="F15" s="1">
-        <v>16804.7</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2995.2</v>
-      </c>
-      <c r="H15" s="1">
-        <v>6659.9</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1057.74</v>
-      </c>
-      <c r="J15" s="1">
-        <v>2539.77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="D16" s="1">
+        <v>2128.1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1630.3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2598.3000000000002</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2191.5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3406.5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>3512.9</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2475.69</v>
+      </c>
+      <c r="K16" s="1">
+        <v>3049.11</v>
+      </c>
+      <c r="L16" s="1">
+        <v>8561.59</v>
+      </c>
+      <c r="M16" s="1">
+        <v>6253.1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>7332</v>
+      </c>
+      <c r="O16" s="10">
+        <v>7842.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1">
-        <v>2128.1</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1630.3</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2598.3000000000002</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2191.5</v>
-      </c>
-      <c r="F16" s="1">
-        <v>3406.5</v>
-      </c>
-      <c r="G16" s="1">
-        <v>3512.9</v>
-      </c>
-      <c r="H16" s="1">
-        <v>2475.69</v>
-      </c>
-      <c r="I16" s="1">
-        <v>3049.11</v>
-      </c>
-      <c r="J16" s="1">
-        <v>8561.59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="D17" s="1">
+        <v>2304.9</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1821.8</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1041.4000000000001</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1704</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2906.4</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2312.8000000000002</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3725.49</v>
+      </c>
+      <c r="K17" s="1">
+        <v>3338.56</v>
+      </c>
+      <c r="L17" s="1">
+        <v>4777.6000000000004</v>
+      </c>
+      <c r="M17" s="1">
+        <v>8997.7000000000007</v>
+      </c>
+      <c r="N17" s="1">
+        <v>16842.099999999999</v>
+      </c>
+      <c r="O17" s="10">
+        <v>13537.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="1">
-        <v>2304.9</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1821.8</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1041.4000000000001</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1704</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2906.4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2312.8000000000002</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3725.49</v>
-      </c>
-      <c r="I17" s="1">
-        <v>3338.56</v>
-      </c>
-      <c r="J17" s="1">
-        <v>4777.6000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="D18" s="1">
+        <v>487.3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>384.5</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1006.7</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1254.3</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1402.4</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1209.5</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1537.08</v>
+      </c>
+      <c r="K18" s="1">
+        <v>3227.65</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5113.6000000000004</v>
+      </c>
+      <c r="M18" s="1">
+        <v>3213.7</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1240.0999999999999</v>
+      </c>
+      <c r="O18" s="10">
+        <v>5229.6000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="1">
-        <v>487.3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>384.5</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1006.7</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1254.3</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1402.4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1209.5</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1537.08</v>
-      </c>
-      <c r="I18" s="1">
-        <v>3227.65</v>
-      </c>
-      <c r="J18" s="1">
-        <v>5113.6000000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="D19" s="1">
+        <v>585.20000000000005</v>
+      </c>
+      <c r="E19" s="1">
+        <v>311.3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>325.3</v>
+      </c>
+      <c r="G19" s="1">
+        <v>445.8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1182.3</v>
+      </c>
+      <c r="I19" s="1">
+        <v>972.4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>552.72</v>
+      </c>
+      <c r="K19" s="1">
+        <v>492.95</v>
+      </c>
+      <c r="L19" s="1">
+        <v>583.71</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1388</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2426.8000000000002</v>
+      </c>
+      <c r="O19" s="1">
+        <v>722.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="1">
-        <v>585.20000000000005</v>
-      </c>
-      <c r="C19" s="1">
-        <v>311.3</v>
-      </c>
-      <c r="D19" s="1">
-        <v>325.3</v>
-      </c>
-      <c r="E19" s="1">
-        <v>445.8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1182.3</v>
-      </c>
-      <c r="G19" s="1">
-        <v>972.4</v>
-      </c>
-      <c r="H19" s="1">
-        <v>552.72</v>
-      </c>
-      <c r="I19" s="1">
-        <v>492.95</v>
-      </c>
-      <c r="J19" s="1">
-        <v>583.71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="1">
+        <v>755.4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1469.2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1008.7</v>
+      </c>
+      <c r="G20" s="1">
+        <v>397</v>
+      </c>
+      <c r="H20" s="1">
+        <v>757.2</v>
+      </c>
+      <c r="I20" s="1">
+        <v>500</v>
+      </c>
+      <c r="J20" s="1">
+        <v>460.76</v>
+      </c>
+      <c r="K20" s="1">
+        <v>530.53</v>
+      </c>
+      <c r="L20" s="1">
+        <v>945.23</v>
+      </c>
+      <c r="M20" s="1">
+        <v>728.2</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1073.4000000000001</v>
+      </c>
+      <c r="O20" s="1">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="5">
-        <v>755.4</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1469.2</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1008.7</v>
-      </c>
-      <c r="E20" s="5">
-        <v>397</v>
-      </c>
-      <c r="F20" s="5">
-        <v>757.2</v>
-      </c>
-      <c r="G20" s="5">
-        <v>500</v>
-      </c>
-      <c r="H20" s="5">
-        <v>460.76</v>
-      </c>
-      <c r="I20" s="5">
-        <v>530.53</v>
-      </c>
-      <c r="J20" s="5">
-        <v>945.23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2">
+        <v>223.3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>712.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2940.1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>988.9</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1430</v>
+      </c>
+      <c r="I21" s="2">
+        <v>3321.8</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2903.78</v>
+      </c>
+      <c r="K21" s="2">
+        <v>3995.01</v>
+      </c>
+      <c r="L21" s="2">
+        <v>3655.83</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5665.5</v>
+      </c>
+      <c r="N21" s="2">
+        <v>4444.5</v>
+      </c>
+      <c r="O21" s="11">
+        <v>3827.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="B21" s="2">
-        <v>223.3</v>
-      </c>
-      <c r="C21" s="2">
-        <v>712.5</v>
-      </c>
-      <c r="D21" s="2">
-        <v>2940.1</v>
-      </c>
-      <c r="E21" s="2">
-        <v>988.9</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1430</v>
-      </c>
-      <c r="G21" s="2">
-        <v>3321.8</v>
-      </c>
-      <c r="H21" s="2">
-        <v>2903.78</v>
-      </c>
-      <c r="I21" s="2">
-        <v>3995.01</v>
-      </c>
-      <c r="J21" s="2">
-        <v>3655.83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
